--- a/mediation_results.xlsx
+++ b/mediation_results.xlsx
@@ -828,19 +828,19 @@
         <v>0.155</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0278</v>
+        <v>0.028</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1074</v>
+        <v>0.106</v>
       </c>
       <c r="H2" t="n">
-        <v>0.217</v>
+        <v>0.2168</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1061</v>
+        <v>0.1053</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2154</v>
+        <v>0.2158</v>
       </c>
       <c r="K2" t="n">
         <v>0.127</v>
@@ -885,16 +885,16 @@
         <v>0.0234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1096</v>
+        <v>0.1099</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2023</v>
+        <v>0.2036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1085</v>
+        <v>0.108</v>
       </c>
       <c r="J3" t="n">
-        <v>0.201</v>
+        <v>0.2012</v>
       </c>
       <c r="K3" t="n">
         <v>0.1454</v>
